--- a/histograms/histogram_avg_s_valence_electrons.xlsx
+++ b/histograms/histogram_avg_s_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>1.43125</v>
       </c>
       <c r="B2" t="n">
-        <v>506</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1.460416666666667</v>
       </c>
       <c r="B3" t="n">
-        <v>983</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>1.489583333333333</v>
       </c>
       <c r="B4" t="n">
-        <v>1274</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>1.51875</v>
       </c>
       <c r="B5" t="n">
-        <v>2017</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>1.547916666666667</v>
       </c>
       <c r="B6" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>1.577083333333333</v>
       </c>
       <c r="B7" t="n">
-        <v>746</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>1.60625</v>
       </c>
       <c r="B8" t="n">
-        <v>728</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>1.635416666666667</v>
       </c>
       <c r="B9" t="n">
-        <v>801</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>1.664583333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         <v>1.722916666666667</v>
       </c>
       <c r="B12" t="n">
-        <v>2008</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>1.752083333333334</v>
       </c>
       <c r="B13" t="n">
-        <v>3097</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>1.78125</v>
       </c>
       <c r="B14" t="n">
-        <v>233</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>1.810416666666667</v>
       </c>
       <c r="B15" t="n">
-        <v>987</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>1.839583333333334</v>
       </c>
       <c r="B16" t="n">
-        <v>333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>1.86875</v>
       </c>
       <c r="B17" t="n">
-        <v>5993</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>1.897916666666667</v>
       </c>
       <c r="B18" t="n">
-        <v>460</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>1.927083333333333</v>
       </c>
       <c r="B19" t="n">
-        <v>659</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>1.95625</v>
       </c>
       <c r="B20" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>1.985416666666667</v>
       </c>
       <c r="B21" t="n">
-        <v>4890</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
